--- a/export_2026-06-10_split-base.xlsx
+++ b/export_2026-06-10_split-base.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12525" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12525" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="PDF资源" sheetId="1" r:id="rId1"/>
@@ -4996,11 +4996,13 @@
   <dimension ref="A1:Q73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="5" max="5" width="24.625" customWidth="1"/>
-    <col min="6" max="6" width="28.25" customWidth="1"/>
+    <col min="5" max="5" width="48.375" customWidth="1"/>
+    <col min="6" max="6" width="23.875" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="11" max="11" width="14.25" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="8" max="8" width="9.375" customWidth="1"/>
+    <col min="11" max="11" width="18.25" customWidth="1"/>
+    <col min="12" max="12" width="20.375" customWidth="1"/>
+    <col min="13" max="14" width="17.125" customWidth="1"/>
     <col min="15" max="15" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
